--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STZ\eclipse-workspace\SwagLabProj_new\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STZ\eclipse-workspace\Swag-Lab-Project\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C1C909-06D9-41BB-8608-4D455DF5D3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E68B3A-4F34-4D39-9821-4F3D1CF0255E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>standard_user</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Third Item Purchase</t>
+  </si>
+  <si>
+    <t>Item to be removed</t>
+  </si>
+  <si>
+    <t>Remove Item</t>
   </si>
 </sst>
 </file>
@@ -187,7 +196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -214,6 +223,7 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -559,7 +569,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5547A6D9-B35F-4592-972E-BF4A3E31F7BE}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" customWidth="1"/>
@@ -613,7 +623,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>11</v>
@@ -623,6 +633,20 @@
       </c>
       <c r="D4" s="10">
         <v>7.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="10">
+        <v>15.99</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STZ\eclipse-workspace\Swag-Lab-Project\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E68B3A-4F34-4D39-9821-4F3D1CF0255E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96B6760-85DA-4D1D-A4E0-5EFA965EE910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>standard_user</t>
   </si>
@@ -101,6 +101,12 @@
   </si>
   <si>
     <t>Remove Item</t>
+  </si>
+  <si>
+    <t>Fourth Item Purchase</t>
+  </si>
+  <si>
+    <t>Sauce Labs Fleece Jacket</t>
   </si>
 </sst>
 </file>
@@ -223,7 +229,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -569,7 +577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5547A6D9-B35F-4592-972E-BF4A3E31F7BE}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" customWidth="1"/>
@@ -636,16 +644,30 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="12">
+        <v>49.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D6" s="10">
         <v>15.99</v>
       </c>
     </row>

--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\STZ\eclipse-workspace\Swag-Lab-Project\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96B6760-85DA-4D1D-A4E0-5EFA965EE910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8F4B50-8C95-4BC7-B005-58D6C1E8B799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3276" windowWidth="21936" windowHeight="8964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>standard_user</t>
   </si>
@@ -107,6 +107,24 @@
   </si>
   <si>
     <t>Sauce Labs Fleece Jacket</t>
+  </si>
+  <si>
+    <t>Add/Remove Item</t>
+  </si>
+  <si>
+    <t>Sauce_Labs_Backpack</t>
+  </si>
+  <si>
+    <t>Sauce_Labs_Bolt_T_Shirt</t>
+  </si>
+  <si>
+    <t>Sauce_Labs_Onesie</t>
+  </si>
+  <si>
+    <t>Sauce_Labs_Fleece_Jacket</t>
+  </si>
+  <si>
+    <t>Item_Element_Name</t>
   </si>
 </sst>
 </file>
@@ -116,7 +134,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +164,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -161,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -197,12 +222,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -229,9 +265,13 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -577,22 +617,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5547A6D9-B35F-4592-972E-BF4A3E31F7BE}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.88671875" customWidth="1"/>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="11"/>
-    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>13</v>
@@ -600,8 +641,14 @@
       <c r="D1" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
@@ -614,8 +661,14 @@
       <c r="D2" s="10">
         <v>29.99</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>15</v>
       </c>
@@ -628,8 +681,11 @@
       <c r="D3" s="10">
         <v>15.99</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>19</v>
       </c>
@@ -642,8 +698,11 @@
       <c r="D4" s="10">
         <v>7.99</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>22</v>
       </c>
@@ -656,8 +715,11 @@
       <c r="D5" s="12">
         <v>49.99</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -670,8 +732,18 @@
       <c r="D6" s="10">
         <v>15.99</v>
       </c>
+      <c r="E6" s="14" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
+  <dataConsolidate/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B6" xr:uid="{4B4253E7-2EC8-4EAB-B532-038E944AB265}">
+      <formula1>$J$1:$J$2</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>